--- a/Expense tracking/expenses.xlsx
+++ b/Expense tracking/expenses.xlsx
@@ -3,7 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="總覽" sheetId="1" r:id="rId1"/>
+    <sheet name="2026-03" sheetId="1" r:id="rId1"/>
+    <sheet name="總覽" sheetId="2" r:id="rId2"/>
+    <sheet name="全部紀錄" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -397,7 +399,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,27 +431,321 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>（尚無紀錄）</v>
+        <v>2026-03-18</v>
       </c>
       <c r="B2" t="str">
-        <v/>
+        <v>13:14</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>餐飲</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>滷味</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F2" t="str">
+        <v>午餐</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B3" t="str">
+        <v>13:14</v>
+      </c>
+      <c r="C3" t="str">
+        <v>飲料</v>
+      </c>
+      <c r="D3" t="str">
+        <v>一手私藏格雷果冰茶</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B4" t="str">
+        <v>22:19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>餐飲</v>
+      </c>
+      <c r="D4" t="str">
+        <v>小林火鍋</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4" t="str">
+        <v>晚餐</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B5" t="str">
+        <v>22:19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>飲料</v>
+      </c>
+      <c r="D5" t="str">
+        <v>可樂</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D7"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>📊 消費總覽</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
+      </c>
+      <c r="C1" t="str">
+        <v/>
+      </c>
+      <c r="D1" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v/>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>總筆數</v>
+      </c>
+      <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3" t="str">
+        <v>總金額</v>
+      </c>
+      <c r="D3">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v/>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>分類</v>
+      </c>
+      <c r="B5" t="str">
+        <v>金額</v>
+      </c>
+      <c r="C5" t="str">
+        <v>佔比</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>餐飲</v>
+      </c>
+      <c r="B6">
+        <v>320</v>
+      </c>
+      <c r="C6" t="str">
+        <v>77.1%</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>飲料</v>
+      </c>
+      <c r="B7">
+        <v>95</v>
+      </c>
+      <c r="C7" t="str">
+        <v>22.9%</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F5"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>date</v>
+      </c>
+      <c r="B1" t="str">
+        <v>time</v>
+      </c>
+      <c r="C1" t="str">
+        <v>category</v>
+      </c>
+      <c r="D1" t="str">
+        <v>item</v>
+      </c>
+      <c r="E1" t="str">
+        <v>amount</v>
+      </c>
+      <c r="F1" t="str">
+        <v>note</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B2" t="str">
+        <v>13:14</v>
+      </c>
+      <c r="C2" t="str">
+        <v>餐飲</v>
+      </c>
+      <c r="D2" t="str">
+        <v>滷味</v>
+      </c>
+      <c r="E2">
+        <v>120</v>
+      </c>
+      <c r="F2" t="str">
+        <v>午餐</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B3" t="str">
+        <v>13:14</v>
+      </c>
+      <c r="C3" t="str">
+        <v>飲料</v>
+      </c>
+      <c r="D3" t="str">
+        <v>一手私藏格雷果冰茶</v>
+      </c>
+      <c r="E3">
+        <v>65</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B4" t="str">
+        <v>22:19</v>
+      </c>
+      <c r="C4" t="str">
+        <v>餐飲</v>
+      </c>
+      <c r="D4" t="str">
+        <v>小林火鍋</v>
+      </c>
+      <c r="E4">
+        <v>200</v>
+      </c>
+      <c r="F4" t="str">
+        <v>晚餐</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2026-03-18</v>
+      </c>
+      <c r="B5" t="str">
+        <v>22:19</v>
+      </c>
+      <c r="C5" t="str">
+        <v>飲料</v>
+      </c>
+      <c r="D5" t="str">
+        <v>可樂</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Expense tracking/expenses.xlsx
+++ b/Expense tracking/expenses.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -509,9 +509,29 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="B6" t="str">
+        <v>18:56</v>
+      </c>
+      <c r="C6" t="str">
+        <v>餐飲</v>
+      </c>
+      <c r="D6" t="str">
+        <v>辛辣雞肉咖哩</v>
+      </c>
+      <c r="E6">
+        <v>462</v>
+      </c>
+      <c r="F6" t="str">
+        <v>晚餐 神燈搓一下</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -559,13 +579,13 @@
         <v>總筆數</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="str">
         <v>總金額</v>
       </c>
       <c r="D3">
-        <v>415</v>
+        <v>877</v>
       </c>
     </row>
     <row r="4">
@@ -601,10 +621,10 @@
         <v>餐飲</v>
       </c>
       <c r="B6">
-        <v>320</v>
+        <v>782</v>
       </c>
       <c r="C6" t="str">
-        <v>77.1%</v>
+        <v>89.2%</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -618,7 +638,7 @@
         <v>95</v>
       </c>
       <c r="C7" t="str">
-        <v>22.9%</v>
+        <v>10.8%</v>
       </c>
       <c r="D7" t="str">
         <v/>
@@ -633,7 +653,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -743,9 +763,29 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2026-03-19</v>
+      </c>
+      <c r="B6" t="str">
+        <v>18:56</v>
+      </c>
+      <c r="C6" t="str">
+        <v>餐飲</v>
+      </c>
+      <c r="D6" t="str">
+        <v>辛辣雞肉咖哩</v>
+      </c>
+      <c r="E6">
+        <v>462</v>
+      </c>
+      <c r="F6" t="str">
+        <v>晚餐 神燈搓一下</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>